--- a/analys/Asset.xlsx
+++ b/analys/Asset.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20373"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A5F98F-FEA5-4805-9FEE-EB6492C62736}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8ACFFF-C4A9-44C8-812A-82976456DBC1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lioness" sheetId="1" r:id="rId1"/>
-    <sheet name="Young Antelope" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
+    <sheet name="Workflow" sheetId="6" r:id="rId1"/>
+    <sheet name="Lioness" sheetId="1" r:id="rId2"/>
+    <sheet name="Young Antelope" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -242,23 +243,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{087128D9-9EBC-4EFA-8F7B-B7A3AF105A3F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FFFB3EB-2486-4E18-9B50-672DF08FB69F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -266,8 +267,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7800975" y="295275"/>
-          <a:ext cx="6838950" cy="4105275"/>
+          <a:off x="314325" y="142875"/>
+          <a:ext cx="3105150" cy="2638425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -301,91 +302,128 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>1. Identity</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Who is this character?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>2. Physical Condition</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What permanently describes this character's body?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>3. Core Skills</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What abilities define this character?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>4. Movement Style</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>How does this character naturally move?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>5. Personality</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>How does this character consistently think and behave?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>6. Behavioral Rules</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What rules should always be followed and what should never happen?</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.1Thu thập ảnh tham khảo</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 2.2│ ▼ Viết Prompt tạo Character</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 2.3│ ▼ Sinh 3 ảnh </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.4│ ▼ Chọn ảnh đẹp nhất</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 2.5│ ▼ Viết Character Info </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3│ ▼ Kiểm thử Character </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4│ ▼ Master Character</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -393,23 +431,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+        <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1392C64-9113-4C4F-86E5-24E69DE20941}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A92D6CF2-2036-4EEF-9E03-2A1397DDD633}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -417,8 +455,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="428625" y="114300"/>
-          <a:ext cx="5934075" cy="5172075"/>
+          <a:off x="3714750" y="190500"/>
+          <a:ext cx="3419475" cy="4019550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -452,91 +490,28 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US"/>
-            <a:t>1. Prompt tạo Character (để Flow sinh ảnh)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Create a realistic adult African lioness for a wildlife documentary.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Appearance:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>A healthy adult female African lion with a lean muscular body, golden-tan short fur, amber eyes, black nose, dark tail tuft, no visible scars, realistic proportions.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Behavior:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Highly experienced hunter. Calm, patient, focused, observant, moves silently with deliberate steps, never rushes, waits for the perfect moment before attacking.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Movement:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Low stalking posture, smooth walking animation, explosive sprint, powerful leap, realistic feline motion.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Personality:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Confident, intelligent, persistent, efficient predator.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Style:</a:t>
-          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>2.1 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Create a full-body portrait of a single adult African lioness standing naturally on the African savanna.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Wildlife documentary photography.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
         <a:p>
           <a:r>
@@ -545,51 +520,91 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>BBC Earth wildlife documentary.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Natural colors.</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
             <a:t>Photorealistic.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Natural morning light.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Full body visible.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Standing still.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No motion blur.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No dust.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No other animals.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
+        <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D3612D7-24ED-40A4-AA34-F65E6FB8C303}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EEB7FAD-5BEE-40A5-A635-E32E9150D362}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -597,8 +612,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7981950" y="371475"/>
-          <a:ext cx="6838950" cy="4105275"/>
+          <a:off x="7677150" y="180975"/>
+          <a:ext cx="2181225" cy="4610100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -634,88 +649,772 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
-            <a:t>1. Identity</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Who is this character?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>2. Physical Condition</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What permanently describes this character's body?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>3. Core Skills</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What abilities define this character?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>4. Movement Style</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>How does this character naturally move?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>5. Personality</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>How does this character consistently think and behave?</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>6. Behavioral Rules</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>What rules should always be followed and what should never happen?</a:t>
+            <a:t>2. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Adult female African lion.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Lean muscular body.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Uniform sandy-golden fur.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Cream-colored underside.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Broad face.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Rounded ears.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Golden amber eyes.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Dark gray nose.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Long tail with a black tuft.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Healthy short fur.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No scars.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No unusual markings.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461F5538-39E9-43AE-960A-D6F51A348693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10296525" y="209550"/>
+          <a:ext cx="4438650" cy="4657725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Với mỗi Character, hãy xây dựng theo mẫu cố định sau:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Species</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Loài chính xác. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Body proportions</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Tỷ lệ cơ thể. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Distinctive features</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Đặc điểm nhận dạng (sừng, tai, đuôi, vằn lông...). </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Coat &amp; colors</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Màu lông và hoa văn. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Movement</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Dáng đi, cách chạy, tư thế đặc trưng. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Behavior</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Tính cách và vai trò trong câu chuyện.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{087128D9-9EBC-4EFA-8F7B-B7A3AF105A3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7334250" y="190500"/>
+          <a:ext cx="6838950" cy="5172075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Với mỗi Character, hãy xây dựng theo mẫu cố định sau:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Species</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Loài chính xác. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Body proportions</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Tỷ lệ cơ thể. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Distinctive features</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Đặc điểm nhận dạng (sừng, tai, đuôi, vằn lông...). </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Coat &amp; colors</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Màu lông và hoa văn. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Movement</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Dáng đi, cách chạy, tư thế đặc trưng. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" b="1"/>
+            <a:t>Behavior</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t> – Tính cách và vai trò trong câu chuyện.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Adult female African lion.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Medium-sized body with a lean, muscular build.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Golden-tan short fur covering the entire body.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Cream-colored chest, throat, belly, and inner legs.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Rounded ears with darker brown edges.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Amber eyes with black eyelids.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Large black nose.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Short white whiskers.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Strong shoulders and powerful hind legs.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Long tail ending with a black tail tuft.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Healthy coat with no scars, injuries, or missing fur.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Natural relaxed posture.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Moves silently with smooth, controlled steps.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN"/>
+            <a:t>Always appears realistic, anatomically accurate, and consistent across all scenes.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1392C64-9113-4C4F-86E5-24E69DE20941}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1228725" y="219075"/>
+          <a:ext cx="5857875" cy="5172075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>1. Prompt tạo Character (để Flow sinh ảnh)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Create a realistic adult African lioness for a wildlife documentary.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Appearance:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>A healthy adult female African lion with a lean muscular body, golden-tan short fur, amber eyes, black nose, dark tail tuft, no visible scars, realistic proportions.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Behavior:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Highly experienced hunter. Calm, patient, focused, observant, moves silently with deliberate steps, never rushes, waits for the perfect moment before attacking.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Movement:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Low stalking posture, smooth walking animation, explosive sprint, powerful leap, realistic feline motion.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Personality:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Confident, intelligent, persistent, efficient predator.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Style:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Ultra realistic.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>BBC Earth wildlife documentary.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Natural colors.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Photorealistic.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D3612D7-24ED-40A4-AA34-F65E6FB8C303}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7448550" y="276225"/>
+          <a:ext cx="6353175" cy="4552950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>A small herd of Thomson's gazelles.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>The herd consists of approximately 12–15 healthy gazelles.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Most are adult Thomson's gazelles with 2–3 younger gazelles.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>All gazelles share the same appearance and markings as the established Thomson's Gazelle character.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>The herd remains loosely grouped with natural spacing of about one to three body lengths between individuals.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>The gazelles are calm, alert, and frequently look in different directions.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Most individuals are grazing with their heads lowered while a few stand watch with heads raised.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>No individuals are running or panicking unless explicitly requested.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>The herd moves together naturally without becoming overcrowded.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Always appears realistic, anatomically accurate, and consistent across all scenes.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -792,74 +1491,55 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Create a realistic young African antelope for a wildlife documentary.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>A healthy juvenile antelope with a slim athletic body, light tan coat with a white underbelly, long slender legs, large alert ears, small developing horns, dark expressive eyes, and natural proportions. Standing on the African savanna in a relaxed pose.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Ultra-realistic, photorealistic wildlife documentary, BBC Earth style, natural lighting, highly detailed fur, authentic anatomy, no humans, no accessories.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN" b="1"/>
-            <a:t>Mục tiêu của prompt này:</a:t>
-          </a:r>
-          <a:endParaRPr lang="vi-VN"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN"/>
-            <a:t>Khóa ngoại hình. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN"/>
-            <a:t>Khóa tuổi. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN"/>
-            <a:t>Khóa loài. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN"/>
-            <a:t>Khóa phong cách hình ảnh. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="vi-VN"/>
-            <a:t>Chưa đề cập đến cuộc săn. </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>A small herd of Thomson's gazelles.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>The herd consists of approximately 12–15 healthy gazelles.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Most are adult Thomson's gazelles with 2–3 younger gazelles.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -868,7 +1548,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1292,6 +1972,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2186B34-6D06-4DA2-8909-CC8FE9E2CC67}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1301,7 +1991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704D166D-6313-4E4D-B8B8-F23E6BCB39E7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1311,7 +2001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B04979-88BB-4881-9AF7-6DC131C0B91F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1321,7 +2011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96D9199-4C4D-4F82-A470-E877E063EC9C}">
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1343,7 +2033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1357,7 +2047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="135" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1371,7 +2061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1385,7 +2075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1399,7 +2089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1413,7 +2103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1427,7 +2117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1441,7 +2131,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1460,7 +2150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92323995-092F-4318-9723-FA13822B3305}">
   <dimension ref="B3:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1479,7 +2169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1490,7 +2180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1501,7 +2191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1512,7 +2202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1523,7 +2213,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
@@ -1534,7 +2224,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
@@ -1545,7 +2235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
@@ -1556,7 +2246,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
